--- a/output/pdf_financials_xlsx/MRZ.xlsx
+++ b/output/pdf_financials_xlsx/MRZ.xlsx
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>36.383329</v>
+        <v>-36.383329</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>40.357492</v>
+        <v>-40.357492</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -6406,49 +6406,49 @@
         <v>2.259578</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>9.150607000000001</v>
+        <v>9.099836</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>14.019377</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>14.823477</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>14.820837</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>15.146472</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>15.418454</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>16.361942</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>16.615061</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>17.354426</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>17.690529</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>17.828859</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>18.362103</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>19.578061</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>20.857327</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>21.930186</v>
       </c>
     </row>
     <row r="93">
@@ -11707,7 +11707,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -12786,7 +12790,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -14387,7 +14395,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14965,7 +14977,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15808,7 +15824,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -40216,10 +40236,10 @@
         </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>12.734165</v>
+        <v>-12.734165</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>16.142997</v>
+        <v>-16.142997</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MRZ.xlsx
+++ b/output/pdf_financials_xlsx/MRZ.xlsx
@@ -1203,25 +1203,25 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.440137</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.286877</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.614748</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.523497</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.628872</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.415492</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.100501</v>
       </c>
     </row>
     <row r="13">
@@ -2349,25 +2349,25 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.646786</v>
+        <v>-7.086923</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.902479</v>
+        <v>-6.189356</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.962584</v>
+        <v>-6.577332</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.081013</v>
+        <v>-5.60451</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-9.796827</v>
+        <v>-10.425699</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-8.921987</v>
+        <v>-9.337479</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-9.952771</v>
+        <v>-10.053272</v>
       </c>
     </row>
     <row r="28">
@@ -2497,25 +2497,25 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.646786</v>
+        <v>-7.086923</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.902479</v>
+        <v>-6.189356</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.962584</v>
+        <v>-6.577332</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.081013</v>
+        <v>-5.60451</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-9.796827</v>
+        <v>-10.425699</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-8.921987</v>
+        <v>-9.337479</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.952771</v>
+        <v>-10.053272</v>
       </c>
     </row>
     <row r="30">
@@ -2789,10 +2789,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>3.653477</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>5.14728</v>
@@ -2909,10 +2907,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>3.653477</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>5.14728</v>
@@ -20810,7 +20806,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -25208,7 +25204,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -25305,7 +25301,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -26467,7 +26463,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -26560,7 +26556,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -30091,7 +30087,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -35891,7 +35887,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -35992,7 +35988,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -37299,7 +37295,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
